--- a/クラス詳細リスト.xlsx
+++ b/クラス詳細リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{987FBBAC-372E-440B-9369-E6DDAA9EBB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4826B73-845B-4A5C-A7A0-92A6A21D1F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="994" activeTab="10" xr2:uid="{177EC157-700D-4250-B950-0E4050FF7972}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="8" xr2:uid="{177EC157-700D-4250-B950-0E4050FF7972}"/>
   </bookViews>
   <sheets>
     <sheet name="インプットマネージャー" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,18 @@
     <sheet name="ゲームマネージャーベース" sheetId="9" r:id="rId8"/>
     <sheet name="タイトルマネージャー" sheetId="10" r:id="rId9"/>
     <sheet name="タイトルUIマネージャー" sheetId="11" r:id="rId10"/>
-    <sheet name="リザルトマネージャー" sheetId="12" r:id="rId11"/>
+    <sheet name="リザルトUIマネージャー" sheetId="13" r:id="rId11"/>
+    <sheet name="リザルトマネージャー" sheetId="12" r:id="rId12"/>
+    <sheet name="インゲームマネージャー" sheetId="14" r:id="rId13"/>
+    <sheet name="インゲームUIマネージャー" sheetId="15" r:id="rId14"/>
+    <sheet name="コリジョンマネージャー" sheetId="16" r:id="rId15"/>
+    <sheet name="ステージマネージャー" sheetId="17" r:id="rId16"/>
+    <sheet name="ステージ床" sheetId="21" r:id="rId17"/>
+    <sheet name="プレイヤー" sheetId="19" r:id="rId18"/>
+    <sheet name="必殺技" sheetId="20" r:id="rId19"/>
+    <sheet name="ボタン" sheetId="22" r:id="rId20"/>
+    <sheet name="カーソル" sheetId="23" r:id="rId21"/>
+    <sheet name="イメージ" sheetId="24" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="107">
   <si>
     <t>自身が取得した入力を渡す</t>
     <rPh sb="0" eb="2">
@@ -556,6 +567,469 @@
   </si>
   <si>
     <t>リザルトマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーンのUIを管理するクラス</t>
+    <rPh sb="11" eb="13">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インゲームマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーンを管理するクラス</t>
+    <rPh sb="7" eb="9">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インゲームUIマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIマネージャーにやらせた方がいいかも？</t>
+    <rPh sb="13" eb="14">
+      <t>ホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIマネージャーにやらせた方がいいかも？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コリジョンマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーンのUIを管理するクラス</t>
+    <rPh sb="10" eb="12">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定を管理するクラス</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Unityがやるしこれいる？と思ってます</t>
+    <rPh sb="15" eb="16">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオブジェクトの配列</t>
+    <rPh sb="10" eb="12">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bool 当たり判定(当たり判定をしたいオブジェクトのインデックス,*2)</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオブジェクトが持っている配列のインデックスを二つ渡すとそれらが当たっているかどうか返す</t>
+    <rPh sb="10" eb="11">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定を持っているオブジェクトをすべてこの配列にぶちこむ</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクト登録(ゲームオブジェクト)</t>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>渡したゲームオブジェクトを子リジョンマネージャーの持つ配列に登録する</t>
+    <rPh sb="0" eb="1">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ床を管理するクラス</t>
+    <rPh sb="4" eb="5">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ床の配列</t>
+    <rPh sb="4" eb="5">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>床の置き方的に二次元配列にしても良い気がする</t>
+    <rPh sb="0" eb="1">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニジゲンハイレツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落ちる(ステージ床の配列のインデックス)</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定したステージ床を落とす</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壊す(ステージ床の配列のインデックス)</t>
+    <rPh sb="0" eb="1">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定したステージ床を壊す</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技のクールタイム</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <rPh sb="0" eb="2">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーが持つ必殺技そのもののクラス</t>
+    <rPh sb="6" eb="7">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isAlive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生存フラグ</t>
+    <rPh sb="0" eb="2">
+      <t>セイゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ床</t>
+    <rPh sb="4" eb="5">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ床そのもののクラス</t>
+    <rPh sb="4" eb="5">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他必要に応じて</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要に応じて</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落ちる</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壊れる</t>
+    <rPh sb="0" eb="1">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このステージ床が落ちる</t>
+    <rPh sb="6" eb="7">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このステージ床が壊れる</t>
+    <rPh sb="6" eb="7">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択、決定ができるUI</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択された()</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択されたときにおこることを書く</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どのボタンを選択しているか表すUI</t>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンの配列</t>
+    <rPh sb="4" eb="6">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どのボタンを選択しているかに応じて位置を変える</t>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示するだけのUIクラス</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この画像を表示する</t>
+    <rPh sb="2" eb="4">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1015,7 +1489,7 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1067,6 +1541,65 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0F99F4-F1E5-45C9-85E0-CBD235EDD498}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65905BBC-23AD-449E-8982-A00C46397A0C}">
   <sheetPr>
     <tabColor theme="0"/>
@@ -1113,9 +1646,479 @@
       <c r="A7" t="s">
         <v>46</v>
       </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C433C-4063-44C9-B319-613254EF13A8}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{401CC4CC-D06B-4408-8470-67A7CA6DFCE4}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07383756-768E-4EC8-B947-AA2334085CC0}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="65.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{215D4C36-410B-4904-8C45-519FC8FCC767}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="39.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FD329A-D21F-4C3A-BE6D-5F12230DE219}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6A72AD-2A5B-4042-8C74-D25C90BD42C8}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E6B6F19-7EFC-4418-88E2-6579D05D8811}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1185,6 +2188,177 @@
       </c>
       <c r="B10" t="s">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD36E4C-3225-4252-BE6C-533A1C93C338}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A8F2DC-83F1-41BD-8814-4D57986381D5}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E81932-6643-4C6C-9A14-303532EC5163}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1586,6 +2760,9 @@
       <c r="A7" t="s">
         <v>46</v>
       </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
